--- a/Exercícios/_ATIVIDADE AULA 4.xlsx
+++ b/Exercícios/_ATIVIDADE AULA 4.xlsx
@@ -259,8 +259,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFFCC00"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -524,9 +524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>248040</xdr:colOff>
+      <xdr:colOff>247680</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>65880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -540,7 +540,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11400120" y="7324920"/>
-          <a:ext cx="6485760" cy="3742560"/>
+          <a:ext cx="6485400" cy="3742200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
